--- a/Docs/Weight Avg Shares per Min.xlsx
+++ b/Docs/Weight Avg Shares per Min.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shazzak/PycharmProjects/HFT/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CAC2D6-52CC-5446-9DAD-99D9A31EBEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B8D526-97B3-4547-B7D3-01D6BE3DA66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="340" yWindow="980" windowWidth="28800" windowHeight="17100" xr2:uid="{FE528B29-E00D-7F4C-B1FE-C7DFFC45366A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Time Left</t>
   </si>
@@ -84,10 +84,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode=";;;"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -146,7 +147,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -156,6 +157,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -178,6 +180,1121 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$D$23:$D$58</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>360</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$23:$E$58</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>66.666666666666671</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>114.28571428571429</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>133.33333333333334</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>145.45454545454547</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>149.99999999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>153.84615384615384</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>157.14285714285714</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>162.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>164.70588235294116</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>166.66666666666666</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>168.42105263157896</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>171.42857142857142</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>172.72727272727272</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>173.91304347826087</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>174.99999999999997</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>175.99999999999997</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>176.92307692307691</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>177.77777777777777</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>178.57142857142856</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>179.31034482758622</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>179.99999999999997</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>180.64516129032259</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>181.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>181.81818181818181</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>182.35294117647058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>182.85714285714286</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>183.33333333333331</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>183.78378378378378</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>181.81818181818181</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>177.77777777777777</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-47AB-BE43-8C6B-3FD78098882D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="378717503"/>
+        <c:axId val="379486207"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="378717503"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="379486207"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="379486207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="378717503"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.64874978127734018"/>
+          <c:y val="5.6133712452610049E-2"/>
+          <c:w val="0.16916688538932634"/>
+          <c:h val="7.8125546806649182E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>793750</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{967E3209-F04E-0F52-21CB-14B549856CDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -497,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220BE582-391B-D740-84FD-CE2A5076ED8C}">
-  <dimension ref="C2:J21"/>
+  <dimension ref="C2:J58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="24.83203125" bestFit="1" customWidth="1"/>
@@ -516,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>360</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -551,15 +1668,15 @@
       </c>
       <c r="E7" s="1">
         <f t="shared" ref="E7:E8" si="0">-G7</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <f>-MIN(I7,H7)</f>
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
         <f>H8+G8</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>15</v>
@@ -574,15 +1691,15 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <f>-MIN(I8,H8)</f>
-        <v>-330</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
         <f>H9+G9</f>
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="I8" s="7">
         <f>360-15-15</f>
@@ -598,15 +1715,15 @@
       </c>
       <c r="E9" s="1">
         <f>-G9</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
         <f>-MIN(I9,H9)</f>
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="H9" s="1">
         <f>D3</f>
-        <v>360</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>15</v>
@@ -618,7 +1735,7 @@
       </c>
       <c r="D12" s="5">
         <f>SUMPRODUCT(D7:D9,E7:E9)/SUM(E7:E9)</f>
-        <v>56.25</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.2">
@@ -635,7 +1752,7 @@
       </c>
       <c r="D14" s="6">
         <f>D12*D13</f>
-        <v>5.625</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.2">
@@ -644,19 +1761,499 @@
       </c>
       <c r="D16" s="8">
         <f>D2/D14</f>
-        <v>177.77777777777777</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
+        <v>66.666666666666671</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D18" t="str">
         <f>IF(D16&lt;=D3,"Normal", "Ramp")</f>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="E22" s="9">
+        <f>D16</f>
+        <v>66.666666666666671</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="dataTable" ref="E23:E58" dt2D="0" dtr="0" r1="D3"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="G23" t="str">
+        <f>IF(E23&lt;=D23,"Normal", "Ramp")</f>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <f>D23+10</f>
+        <v>20</v>
+      </c>
+      <c r="E24" s="6">
+        <v>80</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" ref="G24:G58" si="1">IF(E24&lt;=D24,"Normal", "Ramp")</f>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <f t="shared" ref="D25:D58" si="2">D24+10</f>
+        <v>30</v>
+      </c>
+      <c r="E25" s="6">
+        <v>100</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="E26" s="6">
+        <v>114.28571428571429</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="E27" s="6">
+        <v>125</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="E28" s="6">
+        <v>133.33333333333334</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D29">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="E29" s="6">
+        <v>140</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D30">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="E30" s="6">
+        <v>145.45454545454547</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D31">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="E31" s="6">
+        <v>149.99999999999997</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D32">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="E32" s="6">
+        <v>153.84615384615384</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="E33" s="6">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="E34" s="6">
+        <v>160</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+      <c r="E35" s="6">
+        <v>162.5</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+      <c r="E36" s="6">
+        <v>164.70588235294116</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="E37" s="6">
+        <v>166.66666666666666</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="E38" s="6">
+        <v>168.42105263157896</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="1"/>
+        <v>Ramp</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D39">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="E39" s="6">
+        <v>170</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="1"/>
         <v>Normal</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="E21" s="8"/>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="E40" s="6">
+        <v>171.42857142857142</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D41">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="E41" s="6">
+        <v>172.72727272727272</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D42">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="E42" s="6">
+        <v>173.91304347826087</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D43">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="E43" s="6">
+        <v>174.99999999999997</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D44">
+        <f t="shared" si="2"/>
+        <v>220</v>
+      </c>
+      <c r="E44" s="6">
+        <v>175.99999999999997</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="45" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D45">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
+      <c r="E45" s="6">
+        <v>176.92307692307691</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="46" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D46">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="E46" s="6">
+        <v>177.77777777777777</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="47" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D47">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="E47" s="6">
+        <v>178.57142857142856</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="48" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D48">
+        <f t="shared" si="2"/>
+        <v>260</v>
+      </c>
+      <c r="E48" s="6">
+        <v>179.31034482758622</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D49">
+        <f t="shared" si="2"/>
+        <v>270</v>
+      </c>
+      <c r="E49" s="6">
+        <v>179.99999999999997</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D50">
+        <f t="shared" si="2"/>
+        <v>280</v>
+      </c>
+      <c r="E50" s="6">
+        <v>180.64516129032259</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="51" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D51">
+        <f t="shared" si="2"/>
+        <v>290</v>
+      </c>
+      <c r="E51" s="6">
+        <v>181.25</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="52" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D52">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="E52" s="6">
+        <v>181.81818181818181</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="53" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D53">
+        <f t="shared" si="2"/>
+        <v>310</v>
+      </c>
+      <c r="E53" s="6">
+        <v>182.35294117647058</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="54" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D54">
+        <f t="shared" si="2"/>
+        <v>320</v>
+      </c>
+      <c r="E54" s="6">
+        <v>182.85714285714286</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="55" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D55">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+      <c r="E55" s="6">
+        <v>183.33333333333331</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="56" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D56">
+        <f t="shared" si="2"/>
+        <v>340</v>
+      </c>
+      <c r="E56" s="6">
+        <v>183.78378378378378</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="57" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D57">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="E57" s="6">
+        <v>181.81818181818181</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
+    </row>
+    <row r="58" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D58">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+      <c r="E58" s="6">
+        <v>177.77777777777777</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="1"/>
+        <v>Normal</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>